--- a/DataTables/Datas/questcontext.xlsx
+++ b/DataTables/Datas/questcontext.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F58D0D0-8128-4672-9401-3AB534A4A93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACFC89F-5612-4CEE-A1BF-F6EE840FD16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -116,33 +116,18 @@
   </si>
   <si>
     <t>问问教练现在该干什么</t>
-  </si>
-  <si>
-    <t>问问教练现在该干什么</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无论怎么样让比赛开起来，让你，教练，拳王随便是谁&lt;color=red&gt;挨顿打&lt;/color&gt;就行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12|3|4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>教练心中燃起了火，他要好好教训拳王一下|你挨了顿打，现在比赛重启了|拳王让你打爆了，现在比赛重启了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>观赏一下这场伟大的比赛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>教练这下彻底让拳王打瘪了，真没出息，不过好歹拳赛开起来了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3|-1|-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练让你去拳击馆找他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去拳击馆找教练吧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不惜一切让拳赛开起来</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -192,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -204,7 +189,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -507,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.375" customWidth="1"/>
@@ -608,64 +592,44 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
+    <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B5" s="3">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="3">
+        <v>14</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E5">
+      <c r="G5" s="3">
         <v>5</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5">
+    </row>
+    <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="3">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="54" x14ac:dyDescent="0.15">
-      <c r="B6">
+      <c r="D6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3">
+        <v>15</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="3">
         <v>2</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="27" x14ac:dyDescent="0.15">
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/questcontext.xlsx
+++ b/DataTables/Datas/questcontext.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACFC89F-5612-4CEE-A1BF-F6EE840FD16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8847C2-9084-402D-9433-0C903CEF57C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -127,7 +127,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>不惜一切让拳赛开起来</t>
+    <t>不惜一切让拳赛重新开起来</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到牙，或者找人上去挨揍，或者想想其他办法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16|17|18|19|20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到牙了|教练让人打瘪了|拳王被你干废了|你打完九龙把这里毁了|拳王打完九龙疯了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1|-1|-1|-1|-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -177,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -189,6 +205,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -491,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.375" customWidth="1"/>
@@ -629,7 +646,27 @@
         <v>30</v>
       </c>
       <c r="G6" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="3" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="B7" s="3">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
         <v>2</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/questcontext.xlsx
+++ b/DataTables/Datas/questcontext.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8847C2-9084-402D-9433-0C903CEF57C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785CC87E-6C62-492F-B492-0483767A18A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,10 +127,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>不惜一切让拳赛重新开起来</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>找到牙，或者找人上去挨揍，或者想想其他办法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -144,6 +140,10 @@
   </si>
   <si>
     <t>-1|-1|-1|-1|-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练说要不惜一切让拳赛重新开起来</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -643,10 +643,10 @@
         <v>15</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G6" s="3">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
@@ -654,19 +654,19 @@
         <v>6</v>
       </c>
       <c r="C7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
